--- a/artfynd/A 8756-2024 artfynd.xlsx
+++ b/artfynd/A 8756-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134301600</v>
+        <v>134301594</v>
       </c>
       <c r="B2" t="n">
         <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529497</v>
+        <v>529420</v>
       </c>
       <c r="R2" t="n">
-        <v>6717324</v>
+        <v>6717409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kraftig tallståga.</t>
+          <t>Födosök i tall med det mesta av barken kvar. Hacken vätter mot myren på miljöbilden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134301591</v>
+        <v>134301600</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529413</v>
+        <v>529497</v>
       </c>
       <c r="R3" t="n">
-        <v>6717495</v>
+        <v>6717324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kraftig tallståga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134301599</v>
+        <v>134301591</v>
       </c>
       <c r="B4" t="n">
-        <v>8460</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,28 +926,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529486</v>
+        <v>529413</v>
       </c>
       <c r="R4" t="n">
-        <v>6717318</v>
+        <v>6717495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tre lågor</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1139,6 +1141,778 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134301599</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Korsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>529486</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6717318</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tre lågor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134301582</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Korsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>529549</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6717379</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134301588</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Korsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>529455</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6717548</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134301598</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Korsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>529499</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6717312</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>linnea ekorren</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134301930</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Korsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>529501</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6717246</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134301593</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Korsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>529441</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6717458</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134301595</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>529438</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6717401</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8756-2024 artfynd.xlsx
+++ b/artfynd/A 8756-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301594</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301585</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301599</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301582</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301588</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301598</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1696,6 +1741,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301930</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,8 +1967,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134301595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>